--- a/docs/Panvitium_Economy_Template.xlsx
+++ b/docs/Panvitium_Economy_Template.xlsx
@@ -6580,7 +6580,7 @@
     <row r="9" ht="15" customHeight="1" s="57">
       <c r="A9" s="64" t="inlineStr">
         <is>
-          <t>Black Robe</t>
+          <t>Red Robe</t>
         </is>
       </c>
       <c r="B9" s="67" t="inlineStr">

--- a/docs/Panvitium_Economy_Template.xlsx
+++ b/docs/Panvitium_Economy_Template.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Globals" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Sins &amp; Devotion" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Sigils" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Suasio" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Logos" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Decimatio" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Indagatio &amp; Emptio" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="Maleficia" sheetId="7" state="visible" r:id="rId7"/>
@@ -2118,7 +2118,7 @@
       </c>
       <c r="F6" s="67" t="inlineStr">
         <is>
-          <t>+100% overall Suasio efficiency (mult) /lvl; unlocks Suasio actions and toggles</t>
+          <t>+100% overall Logos efficiency (mult) /lvl; unlocks Logos actions and toggles</t>
         </is>
       </c>
     </row>
@@ -3085,7 +3085,7 @@
       </c>
       <c r="D21" s="81" t="inlineStr">
         <is>
-          <t>-Suasio negative outcome chance</t>
+          <t>-Logos negative outcome chance</t>
         </is>
       </c>
       <c r="E21" s="61" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="D43" s="67" t="inlineStr">
         <is>
-          <t xml:space="preserve"> +chance to duplicate output of Suasio</t>
+          <t xml:space="preserve"> +chance to duplicate output of Logos</t>
         </is>
       </c>
       <c r="E43" s="61" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="D51" s="85" t="inlineStr">
         <is>
-          <t>+Stellar chance for Suasio</t>
+          <t>+Stellar chance for Logos</t>
         </is>
       </c>
       <c r="E51" s="61" t="inlineStr">
@@ -4462,7 +4462,7 @@
       </c>
       <c r="D60" s="77" t="inlineStr">
         <is>
-          <t>+Suasio positive outcome chance</t>
+          <t>+Logos positive outcome chance</t>
         </is>
       </c>
       <c r="E60" s="61" t="inlineStr">
@@ -4990,7 +4990,7 @@
       </c>
       <c r="D75" s="88" t="inlineStr">
         <is>
-          <t>+Suasio action efficiency</t>
+          <t>+Logos action efficiency</t>
         </is>
       </c>
       <c r="E75" s="61" t="inlineStr">
@@ -5069,7 +5069,7 @@
     <row r="1" ht="19.5" customHeight="1" s="57">
       <c r="A1" s="65" t="inlineStr">
         <is>
-          <t>Suasio — Tempting</t>
+          <t>Logos — Tempting</t>
         </is>
       </c>
     </row>
@@ -6733,7 +6733,7 @@
       </c>
       <c r="F13" s="67" t="inlineStr">
         <is>
-          <t>reveal Suasio distribution</t>
+          <t>reveal Logos distribution</t>
         </is>
       </c>
       <c r="G13" s="69" t="inlineStr">
@@ -7067,7 +7067,7 @@
       </c>
       <c r="F23" s="67" t="inlineStr">
         <is>
-          <t>*1.66 Suasio efficiency</t>
+          <t>*1.66 Logos efficiency</t>
         </is>
       </c>
       <c r="G23" s="69" t="inlineStr">
@@ -7234,7 +7234,7 @@
       </c>
       <c r="F28" s="67" t="inlineStr">
         <is>
-          <t>*1.33 Suasio efficiency</t>
+          <t>*1.33 Logos efficiency</t>
         </is>
       </c>
       <c r="G28" s="69" t="inlineStr">
